--- a/outputs/unified/final/q4/problem4_submission.xlsx
+++ b/outputs/unified/final/q4/problem4_submission.xlsx
@@ -4164,7 +4164,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S006,S007,S008,S009,S010,S012,S013,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -4208,11 +4208,11 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>0</v>
@@ -4230,10 +4230,10 @@
         <v>1</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
